--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Disagreement_Stations.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Disagreement_Stations.xlsx
@@ -521,7 +521,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>-1.8679</v>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>-2.1051</v>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>-2.1644</v>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>2.1537</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="L2" s="5" t="n">
-        <v>1.0291</v>
+        <v>2.7251</v>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.0321</v>
+        <v>1.6773</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1.0321</v>
+        <v>1.6773</v>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.0333</v>
+        <v>1.7069</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1.0333</v>
+        <v>1.7069</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.0321</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Standard MK: Z = -1.868. MMK: Z = -1.131 (ΔZ = +0.736; CF = 1.0291; n_eff = 33.0). PW-MK: Z = -1.007 (ΔZ = +0.861). TFPW-MK: Z = -2.123 (ΔZ = -0.255).</t>
+          <t>Standard MK: Z = -1.868. MMK: Z = -1.131 (ΔZ = +0.736; CF = 2.7251; n_eff = 12.5). PW-MK: Z = -1.007 (ΔZ = +0.861). TFPW-MK: Z = -2.123 (ΔZ = -0.255).</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Standard MK: Z = -2.105. MMK: Z = -1.625 (ΔZ = +0.480; CF = 1.0321; n_eff = 32.9). PW-MK: Z = -0.976 (ΔZ = +1.129). TFPW-MK: Z = -2.092 (ΔZ = +0.013).</t>
+          <t>Standard MK: Z = -2.105. MMK: Z = -1.625 (ΔZ = +0.480; CF = 1.6773; n_eff = 20.3). PW-MK: Z = -0.976 (ΔZ = +1.129). TFPW-MK: Z = -2.092 (ΔZ = +0.013).</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>MK and TFPW-MK agree on a significant trend; MMK and PW-MK do not. The MMK correction factor (CF = 1.0321) inflates Var(S) by 3.2%, reducing |Z| from 2.105 to 1.625 and crossing the 1.96 threshold. PW-MK's stronger correction also reduces the Sen's slope from -6.478 to -2.520 mm yr⁻¹ (61% reduction), indicating that PW removes trend signal along with autocorrelation. TFPW-MK preserves the slope at -5.614 mm yr⁻¹ and retains significance.</t>
+          <t>MK and TFPW-MK agree on a significant trend; MMK and PW-MK do not. The MMK correction factor (CF = 1.6773) inflates Var(S) by 67.7%, reducing |Z| from 2.105 to 1.625 and crossing the 1.96 threshold. PW-MK's stronger correction also reduces the Sen's slope from -6.478 to -2.520 mm yr⁻¹ (61% reduction), indicating that PW removes trend signal along with autocorrelation. TFPW-MK preserves the slope at -5.614 mm yr⁻¹ and retains significance.</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Standard MK: Z = -2.164. MMK: Z = -1.657 (ΔZ = +0.508; CF = 1.0333; n_eff = 32.9). PW-MK: Z = -1.193 (ΔZ = +0.971). TFPW-MK: Z = -2.588 (ΔZ = -0.423).</t>
+          <t>Standard MK: Z = -2.164. MMK: Z = -1.657 (ΔZ = +0.508; CF = 1.7069; n_eff = 19.9). PW-MK: Z = -1.193 (ΔZ = +0.971). TFPW-MK: Z = -2.588 (ΔZ = -0.423).</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>MK and TFPW-MK agree on a significant trend; MMK and PW-MK do not. The MMK correction factor (CF = 1.0333) inflates Var(S) by 3.3%, reducing |Z| from 2.164 to 1.657 and crossing the 1.96 threshold. PW-MK's stronger correction also reduces the Sen's slope from -6.544 to -3.009 mm yr⁻¹ (54% reduction), indicating that PW removes trend signal along with autocorrelation. TFPW-MK preserves the slope at -6.289 mm yr⁻¹ and retains significance.</t>
+          <t>MK and TFPW-MK agree on a significant trend; MMK and PW-MK do not. The MMK correction factor (CF = 1.7069) inflates Var(S) by 70.7%, reducing |Z| from 2.164 to 1.657 and crossing the 1.96 threshold. PW-MK's stronger correction also reduces the Sen's slope from -6.544 to -3.009 mm yr⁻¹ (54% reduction), indicating that PW removes trend signal along with autocorrelation. TFPW-MK preserves the slope at -6.289 mm yr⁻¹ and retains significance.</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Standard MK: Z = +2.154. MMK: Z = +2.154 (ΔZ = +0.000; CF = 1.0321; n_eff = 32.0). PW-MK: Z = +1.476 (ΔZ = -0.678). TFPW-MK: Z = +2.154 (ΔZ = +0.000).</t>
+          <t>Standard MK: Z = +2.154. MMK: Z = +2.154 (ΔZ = +0.000; CF = 1.0000; n_eff = 33.0). PW-MK: Z = +1.476 (ΔZ = -0.678). TFPW-MK: Z = +2.154 (ΔZ = +0.000).</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
